--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Practicas\Seguimiento semanal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EAB353-3F38-41E0-867A-BD6B2EE3EA24}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC49507-B050-4964-868A-09DAB257D90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9636" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="29">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -103,6 +103,12 @@
   </si>
   <si>
     <t>Esquematizar las mejores de la web del MUJA para ver donde poder meter la IA, y inicio a hacer  la pagina web</t>
+  </si>
+  <si>
+    <t>Continuado de la pagina web y busqueda de IA</t>
+  </si>
+  <si>
+    <t>5h</t>
   </si>
 </sst>
 </file>
@@ -265,6 +271,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -277,18 +295,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
@@ -296,57 +302,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -497,6 +452,57 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -514,12 +520,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -529,12 +535,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -544,12 +550,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -779,52 +785,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.90625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.88671875" style="1"/>
-    <col min="14" max="14" width="8.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="24.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.453125" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="1"/>
+    <col min="14" max="14" width="8.90625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -847,7 +853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -870,7 +876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -890,7 +896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -910,7 +916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -930,213 +936,226 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C11" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1162,52 +1181,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.08984375" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.88671875" style="8"/>
-    <col min="14" max="14" width="8.88671875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="8"/>
+    <col min="7" max="7" width="24.36328125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.453125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="8"/>
+    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1230,7 +1249,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1253,7 +1272,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1273,7 +1292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1293,7 +1312,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1313,219 +1332,232 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C11" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="D11" s="12">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1551,52 +1583,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.88671875" style="8"/>
-    <col min="14" max="14" width="8.88671875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="8"/>
+    <col min="7" max="7" width="24.36328125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.453125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="8"/>
+    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1619,7 +1651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1642,7 +1674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1662,7 +1694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1682,7 +1714,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1702,207 +1734,222 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="5"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B11" s="5">
+        <v>46122</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="8">
+        <v>4</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC49507-B050-4964-868A-09DAB257D90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3206A1D8-FD88-48B1-979E-016148D5FAED}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9636" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="33">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -109,6 +109,18 @@
   </si>
   <si>
     <t>5h</t>
+  </si>
+  <si>
+    <t>Finalizacion del presupuesto para el MUMI</t>
+  </si>
+  <si>
+    <t>8.25</t>
+  </si>
+  <si>
+    <t>Videos IA y presupuesto</t>
+  </si>
+  <si>
+    <t>PDF videos y presupuesto</t>
   </si>
 </sst>
 </file>
@@ -271,6 +283,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -283,18 +307,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
@@ -302,6 +314,57 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -452,57 +515,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -520,12 +532,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -535,12 +547,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -550,12 +562,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -785,52 +797,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.36328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.453125" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="1"/>
-    <col min="14" max="14" width="8.90625" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="1"/>
+    <col min="7" max="7" width="24.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.44140625" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.88671875" style="1"/>
+    <col min="14" max="14" width="8.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -853,7 +865,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -876,7 +888,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -896,7 +908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -916,7 +928,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -936,7 +948,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -956,206 +968,219 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="C12" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1181,52 +1206,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.08984375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.109375" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.36328125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.453125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="8"/>
-    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="8"/>
+    <col min="7" max="7" width="24.33203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.44140625" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.88671875" style="8"/>
+    <col min="14" max="14" width="8.88671875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1249,7 +1274,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1272,7 +1297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1292,7 +1317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1312,7 +1337,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1332,7 +1357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1352,212 +1377,225 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="C12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="8">
+        <v>6</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1583,52 +1621,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.36328125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.453125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="8"/>
-    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="8"/>
+    <col min="7" max="7" width="24.33203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.44140625" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.88671875" style="8"/>
+    <col min="14" max="14" width="8.88671875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1651,7 +1689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1674,7 +1712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1694,7 +1732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1714,7 +1752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1734,7 +1772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1754,202 +1792,217 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="5"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="5">
+        <v>46125</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="8">
+        <v>6</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Presencial\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3206A1D8-FD88-48B1-979E-016148D5FAED}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9636" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9510" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="33">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -114,19 +113,19 @@
     <t>Finalizacion del presupuesto para el MUMI</t>
   </si>
   <si>
-    <t>8.25</t>
-  </si>
-  <si>
     <t>Videos IA y presupuesto</t>
   </si>
   <si>
     <t>PDF videos y presupuesto</t>
+  </si>
+  <si>
+    <t>Creacion de los prmeros videos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
@@ -529,45 +528,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
-  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla811" displayName="Tabla811" ref="B6:G51">
+  <autoFilter ref="B6:G51"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
-  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla810" displayName="Tabla810" ref="B6:G51">
+  <autoFilter ref="B6:G51"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
-  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla8" displayName="Tabla8" ref="B6:G51">
+  <autoFilter ref="B6:G51"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -795,22 +794,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.88671875" style="1"/>
-    <col min="14" max="14" width="8.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="24.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.85546875" style="1"/>
+    <col min="14" max="14" width="8.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -822,10 +821,10 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -837,12 +836,12 @@
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -865,7 +864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -888,7 +887,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -908,7 +907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -928,7 +927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -948,7 +947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -968,7 +967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -979,208 +978,221 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="1">
-        <v>6</v>
+        <v>31</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C13" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1191,7 +1203,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51" xr:uid="{0006000E-00C8-433F-B010-002400400074}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -1204,22 +1216,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.140625" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.88671875" style="8"/>
-    <col min="14" max="14" width="8.88671875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="8"/>
+    <col min="7" max="7" width="24.28515625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.85546875" style="8"/>
+    <col min="14" max="14" width="8.85546875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
@@ -1231,10 +1243,10 @@
       <c r="F2" s="19"/>
       <c r="G2" s="19"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
@@ -1246,12 +1258,12 @@
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1274,7 +1286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1297,7 +1309,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1317,7 +1329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1337,7 +1349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1357,7 +1369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1377,225 +1389,238 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>30</v>
+      <c r="C12" s="12">
+        <v>0.35069444444444442</v>
       </c>
       <c r="D12" s="12">
         <v>0.60069444444444442</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="8">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C13" s="12">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1606,7 +1631,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51" xr:uid="{008700E8-0054-4E83-8319-002300310070}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -1619,22 +1644,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.88671875" style="8"/>
-    <col min="14" max="14" width="8.88671875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="8"/>
+    <col min="7" max="7" width="24.28515625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.85546875" style="8"/>
+    <col min="14" max="14" width="8.85546875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
@@ -1646,10 +1671,10 @@
       <c r="F2" s="19"/>
       <c r="G2" s="19"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
@@ -1661,12 +1686,12 @@
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1689,7 +1714,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1712,7 +1737,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1732,7 +1757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1752,7 +1777,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1772,7 +1797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1792,7 +1817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1812,197 +1837,218 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="5"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="5"/>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
+        <v>46126</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="8">
+        <v>6</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>46127</v>
+      </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="5"/>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
+        <v>46128</v>
+      </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>46129</v>
+      </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -2013,7 +2059,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51" xr:uid="{00350053-0040-4CE7-BA75-00E90007004B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Presencial\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC9F1732-BE90-4ECB-B2CD-A67F5F5BDD10}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9510" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26083" windowHeight="11330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="34">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -120,12 +121,15 @@
   </si>
   <si>
     <t>Creacion de los prmeros videos</t>
+  </si>
+  <si>
+    <t>Guionizacion de los videos, hoja de personajes e historia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
@@ -528,45 +532,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla811" displayName="Tabla811" ref="B6:G51">
-  <autoFilter ref="B6:G51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
+  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla810" displayName="Tabla810" ref="B6:G51">
-  <autoFilter ref="B6:G51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
+  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla8" displayName="Tabla8" ref="B6:G51">
-  <autoFilter ref="B6:G51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
+  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -794,19 +798,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.85546875" style="1"/>
-    <col min="14" max="14" width="8.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="7" width="24.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="1"/>
+    <col min="14" max="14" width="8.875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
@@ -1203,7 +1207,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -1216,19 +1220,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.125" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.85546875" style="8"/>
-    <col min="14" max="14" width="8.85546875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.85546875" style="8"/>
+    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="8"/>
+    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="8"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
@@ -1631,7 +1635,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -1644,19 +1648,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.85546875" style="8"/>
-    <col min="14" max="14" width="8.85546875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.85546875" style="8"/>
+    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="8"/>
+    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="8"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
@@ -1861,8 +1865,21 @@
       <c r="B14" s="5">
         <v>46127</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
+      <c r="C14" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0.625</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="8">
+        <v>5</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
@@ -2059,7 +2076,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC9F1732-BE90-4ECB-B2CD-A67F5F5BDD10}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F042E8D4-EE3A-40AC-86D7-4A26DF33D6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26083" windowHeight="11330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="34">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Iván Álvarez López</t>
   </si>
   <si>
-    <t>4,5h</t>
-  </si>
-  <si>
     <t>Alex Gonzalez Garcia</t>
   </si>
   <si>
@@ -124,6 +121,9 @@
   </si>
   <si>
     <t>Guionizacion de los videos, hoja de personajes e historia</t>
+  </si>
+  <si>
+    <t>5,5h</t>
   </si>
 </sst>
 </file>
@@ -271,21 +271,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -298,18 +309,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
@@ -317,57 +316,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -518,6 +466,57 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -535,12 +534,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -550,12 +549,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -565,12 +564,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -800,52 +799,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.90625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="1"/>
-    <col min="14" max="14" width="8.875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="1"/>
+    <col min="7" max="7" width="24.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="1"/>
+    <col min="14" max="14" width="8.90625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -868,7 +867,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -891,7 +890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -911,7 +910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -931,7 +930,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -951,7 +950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -965,13 +964,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -982,7 +981,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>13</v>
@@ -991,7 +990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1002,7 +1001,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>13</v>
@@ -1011,192 +1010,207 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B14" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1222,52 +1236,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.08984375" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="8"/>
-    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="8"/>
+    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="8"/>
+    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1290,7 +1304,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1300,10 +1314,10 @@
       <c r="D7" s="12">
         <v>0.10416666666666667</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -1313,7 +1327,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1326,34 +1340,34 @@
       <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
       <c r="C9" s="12">
-        <v>0.41666666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D9" s="12">
-        <v>8.3333333333333329E-2</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>17</v>
+      <c r="F9" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1361,19 +1375,19 @@
         <v>0.375</v>
       </c>
       <c r="D10" s="12">
-        <v>6.25E-2</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>21</v>
+      <c r="F10" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1383,17 +1397,17 @@
       <c r="D11" s="12">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1404,7 +1418,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>13</v>
@@ -1413,7 +1427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1423,8 +1437,8 @@
       <c r="D13" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>32</v>
+      <c r="E13" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>13</v>
@@ -1433,198 +1447,211 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C14" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1650,52 +1677,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="8"/>
-    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="8"/>
+    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="8"/>
+    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1718,7 +1745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1729,7 +1756,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="8">
         <v>6</v>
@@ -1741,7 +1768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1752,7 +1779,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="8">
         <v>6</v>
@@ -1761,7 +1788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1772,7 +1799,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" s="8">
         <v>4</v>
@@ -1781,7 +1808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1792,7 +1819,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="8">
         <v>4</v>
@@ -1801,7 +1828,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1812,7 +1839,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="8">
         <v>4</v>
@@ -1821,7 +1848,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1832,7 +1859,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" s="8">
         <v>6</v>
@@ -1841,7 +1868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1851,8 +1878,8 @@
       <c r="D13" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>32</v>
+      <c r="E13" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="F13" s="8">
         <v>6</v>
@@ -1861,7 +1888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1872,7 +1899,7 @@
         <v>0.625</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="8">
         <v>5</v>
@@ -1881,191 +1908,191 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F042E8D4-EE3A-40AC-86D7-4A26DF33D6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC78141-D615-412E-896C-4B78C11D42F8}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26083" windowHeight="11330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="36">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -87,30 +87,15 @@
     <t>Iván Álvarez López</t>
   </si>
   <si>
+    <t>4,5h</t>
+  </si>
+  <si>
     <t>Alex Gonzalez Garcia</t>
   </si>
   <si>
-    <t>Decision del tema del proyecto con ayuda de Francisco</t>
-  </si>
-  <si>
-    <t>Visualizacion de posibles mejoras de la web del MUMI con IA</t>
-  </si>
-  <si>
-    <t>Empezar a generar los prompts de los videos de la IA</t>
-  </si>
-  <si>
-    <t>Esquematizar las mejores de la web del MUJA para ver donde poder meter la IA, y inicio a hacer  la pagina web</t>
-  </si>
-  <si>
-    <t>Continuado de la pagina web y busqueda de IA</t>
-  </si>
-  <si>
     <t>5h</t>
   </si>
   <si>
-    <t>Finalizacion del presupuesto para el MUMI</t>
-  </si>
-  <si>
     <t>Videos IA y presupuesto</t>
   </si>
   <si>
@@ -120,10 +105,31 @@
     <t>Creacion de los prmeros videos</t>
   </si>
   <si>
-    <t>Guionizacion de los videos, hoja de personajes e historia</t>
-  </si>
-  <si>
-    <t>5,5h</t>
+    <t>Análisis de posibles ideas y selección final del tema del proyecto, con orientación y asesoramiento de Francisco.</t>
+  </si>
+  <si>
+    <t>Identificación de posibles mejoras en la web del MUMI mediante el uso de herramientas de IA.</t>
+  </si>
+  <si>
+    <t>Inicio de la elaboración de prompts para la generación de vídeos mediante herramientas de IA.</t>
+  </si>
+  <si>
+    <t>Esquematización de las principales secciones de la web del MUJA para identificar posibles integraciones de IA, e inicio del desarrollo de la página web.</t>
+  </si>
+  <si>
+    <t>Continuación del desarrollo de la página web y búsqueda de herramientas de IA aplicables al proyecto.</t>
+  </si>
+  <si>
+    <t>Elaboración y finalización del presupuesto del proyecto para el MUMI.</t>
+  </si>
+  <si>
+    <t>Producción de los primeros vídeos del proyecto utilizando herramientas de inteligencia artificial.</t>
+  </si>
+  <si>
+    <t>Desarrollo de la guionización de los vídeos, junto con la creación de la hoja de personajes y la definición de la narrativa.</t>
+  </si>
+  <si>
+    <t>Desarrollo de la hoja de personajes y ampliación de la guionización de los vídeos, afrontando dificultades en la generación de historias atractivas mediante IA.</t>
   </si>
 </sst>
 </file>
@@ -271,20 +277,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -297,18 +316,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
@@ -316,6 +323,57 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -466,57 +524,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -534,12 +541,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -549,12 +556,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -564,12 +571,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -799,52 +806,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.36328125" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="1"/>
-    <col min="14" max="14" width="8.90625" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="1"/>
+    <col min="7" max="7" width="24.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="1"/>
+    <col min="14" max="14" width="8.875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -867,7 +874,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -890,7 +897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -910,7 +917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -930,7 +937,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -950,7 +957,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -964,13 +971,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -981,7 +988,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>13</v>
@@ -990,7 +997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1001,7 +1008,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>13</v>
@@ -1010,207 +1017,192 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="5">
-        <v>46127</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.35069444444444442</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1236,52 +1228,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.08984375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.125" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="8"/>
-    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="8"/>
+    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="8"/>
+    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1304,7 +1296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1314,10 +1306,10 @@
       <c r="D7" s="12">
         <v>0.10416666666666667</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -1327,7 +1319,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1340,34 +1332,34 @@
       <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
       <c r="C9" s="12">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D9" s="12">
-        <v>0.10416666666666667</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>33</v>
+      <c r="F9" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1375,19 +1367,19 @@
         <v>0.375</v>
       </c>
       <c r="D10" s="12">
-        <v>0.10416666666666667</v>
+        <v>6.25E-2</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>33</v>
+      <c r="F10" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1397,17 +1389,17 @@
       <c r="D11" s="12">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1418,7 +1410,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>13</v>
@@ -1427,7 +1419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1437,8 +1429,8 @@
       <c r="D13" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>31</v>
+      <c r="E13" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>13</v>
@@ -1447,211 +1439,198 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
-      <c r="C14" s="12">
-        <v>0.375</v>
-      </c>
-      <c r="D14" s="12">
-        <v>0.60069444444444442</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1677,52 +1656,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="8"/>
-    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="8"/>
+    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="8"/>
+    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="C2" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1745,7 +1724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1756,7 +1735,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F7" s="8">
         <v>6</v>
@@ -1768,7 +1747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1779,7 +1758,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F8" s="8">
         <v>6</v>
@@ -1788,7 +1767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1799,7 +1778,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" s="8">
         <v>4</v>
@@ -1808,7 +1787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1819,7 +1798,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F10" s="8">
         <v>4</v>
@@ -1828,7 +1807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1839,7 +1818,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F11" s="8">
         <v>4</v>
@@ -1848,7 +1827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1859,7 +1838,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F12" s="8">
         <v>6</v>
@@ -1868,7 +1847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1878,8 +1857,8 @@
       <c r="D13" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>31</v>
+      <c r="E13" s="13" t="s">
+        <v>33</v>
       </c>
       <c r="F13" s="8">
         <v>6</v>
@@ -1888,7 +1867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1899,7 +1878,7 @@
         <v>0.625</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14" s="8">
         <v>5</v>
@@ -1908,191 +1887,204 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="C15" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="8">
+        <v>4</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC78141-D615-412E-896C-4B78C11D42F8}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92114CC-7085-40B3-AD3A-45D81583ED21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26083" windowHeight="11330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t>Desarrollo de la hoja de personajes y ampliación de la guionización de los vídeos, afrontando dificultades en la generación de historias atractivas mediante IA.</t>
+  </si>
+  <si>
+    <t>5,5h</t>
+  </si>
+  <si>
+    <t>Creacion de los segundos videos</t>
   </si>
 </sst>
 </file>
@@ -277,21 +283,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -304,18 +321,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
@@ -323,57 +328,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -524,6 +478,57 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -541,12 +546,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -556,12 +561,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -571,12 +576,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -806,52 +811,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.90625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="1"/>
-    <col min="14" max="14" width="8.875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="1"/>
+    <col min="7" max="7" width="24.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="1"/>
+    <col min="14" max="14" width="8.90625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -874,7 +879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -897,7 +902,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -917,7 +922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -937,7 +942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -957,7 +962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -977,7 +982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -997,7 +1002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1017,192 +1022,222 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B14" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B15" s="5">
+        <v>46128</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1228,52 +1263,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.08984375" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="8"/>
-    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="8"/>
+    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="8"/>
+    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1296,7 +1331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1306,10 +1341,10 @@
       <c r="D7" s="12">
         <v>0.10416666666666667</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -1319,7 +1354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1332,14 +1367,14 @@
       <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1352,14 +1387,14 @@
       <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1372,14 +1407,14 @@
       <c r="E10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1389,7 +1424,7 @@
       <c r="D11" s="12">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="8" t="s">
@@ -1399,7 +1434,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1419,7 +1454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1429,7 +1464,7 @@
       <c r="D13" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="8" t="s">
@@ -1439,198 +1474,224 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C14" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C15" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1656,52 +1717,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="8"/>
-    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="8"/>
+    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="8"/>
+    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1724,7 +1785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1747,7 +1808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1767,7 +1828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1787,7 +1848,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1807,7 +1868,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1827,7 +1888,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1847,7 +1908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1857,7 +1918,7 @@
       <c r="D13" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F13" s="8">
@@ -1867,7 +1928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1887,7 +1948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1907,184 +1968,184 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92114CC-7085-40B3-AD3A-45D81583ED21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D978265-FA6B-49F1-964F-2B3B3442E38C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26083" windowHeight="11330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="39">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Creacion de los segundos videos</t>
+  </si>
+  <si>
+    <t>Continuar con las hojas de personajes, perfeccionar a los personajes y sus historias.</t>
   </si>
 </sst>
 </file>
@@ -297,6 +300,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -309,18 +324,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
@@ -328,6 +331,57 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -478,57 +532,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -546,12 +549,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -561,12 +564,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -576,12 +579,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -811,52 +814,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.36328125" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="1"/>
-    <col min="14" max="14" width="8.90625" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="1"/>
+    <col min="7" max="7" width="24.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="1"/>
+    <col min="14" max="14" width="8.875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -879,7 +882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -902,7 +905,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -922,7 +925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -942,7 +945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -962,7 +965,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -982,7 +985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1002,7 +1005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1022,7 +1025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1042,7 +1045,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1062,182 +1065,182 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1263,52 +1266,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.08984375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.125" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="8"/>
-    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="8"/>
+    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="8"/>
+    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1331,7 +1334,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1354,7 +1357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1374,7 +1377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1414,7 +1417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1434,7 +1437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1454,7 +1457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1474,7 +1477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1494,7 +1497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1514,184 +1517,184 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1717,52 +1720,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.90625" style="8"/>
-    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="8"/>
+    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="8"/>
+    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1785,7 +1788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1808,7 +1811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1828,7 +1831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1848,7 +1851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1888,7 +1891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1908,7 +1911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1945,10 +1948,10 @@
         <v>5</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1968,184 +1971,197 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C16" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="8">
+        <v>4</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D978265-FA6B-49F1-964F-2B3B3442E38C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8112A37E-DFDC-4EF4-8D0A-20C52DE8481E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26083" windowHeight="11330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="39">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -300,6 +300,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -312,18 +324,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
@@ -331,57 +331,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -532,6 +481,57 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -549,12 +549,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -564,12 +564,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -579,12 +579,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
   <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -814,52 +814,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.90625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="1"/>
-    <col min="14" max="14" width="8.875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="1"/>
+    <col min="7" max="7" width="24.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="1"/>
+    <col min="14" max="14" width="8.90625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -882,7 +882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -905,7 +905,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -925,7 +925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -945,7 +945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -965,7 +965,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -985,7 +985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1065,182 +1065,182 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1266,52 +1266,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.08984375" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="8"/>
-    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="8"/>
+    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="8"/>
+    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1517,184 +1517,197 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1720,52 +1733,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.375" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.875" style="8"/>
-    <col min="14" max="14" width="8.875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="8"/>
+    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.36328125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.90625" style="8"/>
+    <col min="14" max="14" width="8.90625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1788,7 +1801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1811,7 +1824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1831,7 +1844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1851,7 +1864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1871,7 +1884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1891,7 +1904,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1911,7 +1924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1931,7 +1944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1951,7 +1964,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1971,7 +1984,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
@@ -1991,177 +2004,177 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="5"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="5"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Presencial\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C102826-CC7B-4AE2-9D1E-59D8E324535A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="46">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -150,12 +151,21 @@
   </si>
   <si>
     <t>Creacion de videos y edición de los mismos</t>
+  </si>
+  <si>
+    <t>Retoques videos y HTML</t>
+  </si>
+  <si>
+    <t>5,5H</t>
+  </si>
+  <si>
+    <t>Edicion de videos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
@@ -297,21 +307,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -558,45 +567,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla811" displayName="Tabla811" ref="B6:G51">
-  <autoFilter ref="B6:G51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla811" displayName="Tabla811" ref="B6:G51">
+  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Fecha" dataDxfId="17"/>
-    <tableColumn id="2" name="Hora inicio" dataDxfId="16"/>
-    <tableColumn id="3" name="Hora fin" dataDxfId="15"/>
-    <tableColumn id="4" name="Tareas realizadas" dataDxfId="14"/>
-    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="13"/>
-    <tableColumn id="6" name="Lugar de realización" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora inicio" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora fin" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tareas realizadas" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tiempo dedicado (h)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Lugar de realización" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla810" displayName="Tabla810" ref="B6:G51">
-  <autoFilter ref="B6:G51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla810" displayName="Tabla810" ref="B6:G51">
+  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Fecha" dataDxfId="11"/>
-    <tableColumn id="2" name="Hora inicio" dataDxfId="10"/>
-    <tableColumn id="3" name="Hora fin" dataDxfId="9"/>
-    <tableColumn id="4" name="Tareas realizadas" dataDxfId="8"/>
-    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="7"/>
-    <tableColumn id="6" name="Lugar de realización" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Hora inicio" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora fin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Tareas realizadas" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tiempo dedicado (h)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Lugar de realización" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla8" displayName="Tabla8" ref="B6:G51">
-  <autoFilter ref="B6:G51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla8" displayName="Tabla8" ref="B6:G51">
+  <autoFilter ref="B6:G51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Fecha" dataDxfId="5"/>
-    <tableColumn id="2" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="3" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="4" name="Tareas realizadas" dataDxfId="2"/>
-    <tableColumn id="5" name="Tiempo dedicado (h)" dataDxfId="1"/>
-    <tableColumn id="6" name="Lugar de realización" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Hora inicio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Hora fin" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tareas realizadas" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Tiempo dedicado (h)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Lugar de realización" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -824,54 +833,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" style="1" customWidth="1"/>
-    <col min="9" max="13" width="8.85546875" style="1"/>
-    <col min="14" max="14" width="8.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="7" width="24.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.453125" style="1" customWidth="1"/>
+    <col min="9" max="13" width="8.81640625" style="1"/>
+    <col min="14" max="14" width="8.81640625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -894,7 +903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -917,7 +926,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -937,7 +946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -957,7 +966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -977,7 +986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -997,7 +1006,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1017,7 +1026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1037,7 +1046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1057,7 +1066,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1077,7 +1086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="7">
         <v>46129</v>
       </c>
@@ -1097,7 +1106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="7">
         <v>46132</v>
       </c>
@@ -1117,7 +1126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" s="7">
         <v>46133</v>
       </c>
@@ -1137,167 +1146,182 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="7"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="7">
+        <v>46134</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="7"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="7"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="7"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="7"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="7"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="7"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="7"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="7"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="7"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="7"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="7"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="7"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="7"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1308,7 +1332,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G15 G17:G51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G15 G17:G51" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -1321,54 +1345,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47.140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.1796875" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.85546875" style="8"/>
-    <col min="14" max="14" width="8.85546875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.85546875" style="8"/>
+    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.453125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.81640625" style="8"/>
+    <col min="14" max="14" width="8.81640625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1391,7 +1415,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1414,7 +1438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1434,7 +1458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1454,7 +1478,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1474,7 +1498,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1494,7 +1518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -1514,7 +1538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -1524,7 +1548,7 @@
       <c r="D13" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="8" t="s">
@@ -1534,7 +1558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -1544,7 +1568,7 @@
       <c r="D14" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="8" t="s">
@@ -1554,7 +1578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -1574,7 +1598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
@@ -1594,7 +1618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="5">
         <v>46132</v>
       </c>
@@ -1604,17 +1628,17 @@
       <c r="D17" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" s="5">
         <v>46133</v>
       </c>
@@ -1624,7 +1648,7 @@
       <c r="D18" s="12">
         <v>0.60069444444444442</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="8" t="s">
         <v>30</v>
       </c>
       <c r="F18" s="8" t="s">
@@ -1634,173 +1658,186 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="5">
         <v>46134</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C19" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="D19" s="12">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="5">
         <v>46135</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="5">
         <v>46136</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -1811,7 +1848,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -1824,54 +1861,54 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
     <col min="2" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="40" style="8" customWidth="1"/>
     <col min="6" max="6" width="20" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" style="8" customWidth="1"/>
-    <col min="9" max="13" width="8.85546875" style="8"/>
-    <col min="14" max="14" width="8.85546875" style="8" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.85546875" style="8"/>
+    <col min="7" max="7" width="24.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.453125" style="8" customWidth="1"/>
+    <col min="9" max="13" width="8.81640625" style="8"/>
+    <col min="14" max="14" width="8.81640625" style="8" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1894,7 +1931,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>46118</v>
       </c>
@@ -1917,7 +1954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>46119</v>
       </c>
@@ -1937,7 +1974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46120</v>
       </c>
@@ -1957,7 +1994,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>46121</v>
       </c>
@@ -1977,7 +2014,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>46122</v>
       </c>
@@ -1997,7 +2034,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>46125</v>
       </c>
@@ -2017,7 +2054,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>46126</v>
       </c>
@@ -2037,7 +2074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46127</v>
       </c>
@@ -2057,7 +2094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>46128</v>
       </c>
@@ -2077,7 +2114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>46129</v>
       </c>
@@ -2097,7 +2134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="5">
         <v>46132</v>
       </c>
@@ -2107,7 +2144,7 @@
       <c r="D17" s="12">
         <v>0.5625</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="8" t="s">
         <v>39</v>
       </c>
       <c r="F17" s="8">
@@ -2117,7 +2154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" s="5">
         <v>46133</v>
       </c>
@@ -2137,173 +2174,186 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="5">
         <v>46134</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C19" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0.625</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="8">
+        <v>5</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="5">
         <v>46135</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="5">
         <v>46136</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="5"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="5"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="5"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="5"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="5"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="5"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="5"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="5"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="5"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B46" s="5"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B48" s="5"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="5"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B51" s="5"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -2314,7 +2364,7 @@
     <mergeCell ref="C4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G51" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$N$5:$N$7</formula1>
     </dataValidation>
   </dataValidations>

--- a/registro_estancias.xlsx
+++ b/registro_estancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C102826-CC7B-4AE2-9D1E-59D8E324535A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2ECF9A-C1B2-42EF-9FDE-007EED162064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mara" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="46">
   <si>
     <t>Alumno/a:</t>
   </si>
@@ -156,10 +156,10 @@
     <t>Retoques videos y HTML</t>
   </si>
   <si>
-    <t>5,5H</t>
-  </si>
-  <si>
     <t>Edicion de videos</t>
+  </si>
+  <si>
+    <t>Creacion del video final</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1157,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>13</v>
@@ -1167,14 +1167,44 @@
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B20" s="7"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+      <c r="B20" s="7">
+        <v>46135</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B21" s="7"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="B21" s="7">
+        <v>46136</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="7"/>
@@ -1672,7 +1702,7 @@
         <v>43</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>11</v>
@@ -1682,15 +1712,41 @@
       <c r="B20" s="5">
         <v>46135</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="C20" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="D20" s="12">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="5">
         <v>46136</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="C21" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="D21" s="12">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
@@ -2198,15 +2254,41 @@
       <c r="B20" s="5">
         <v>46135</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="C20" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D20" s="12">
+        <v>0.625</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="8">
+        <v>5</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="5">
         <v>46136</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="C21" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="8">
+        <v>4</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
